--- a/accountant-skill/data/input/journals/payroll_journal.xlsx
+++ b/accountant-skill/data/input/journals/payroll_journal.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>61000</v>
+        <v>53000</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>10100</v>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>61000</v>
+        <v>53000</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>10100</v>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>61000</v>
+        <v>53000</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>10100</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>61000</v>
+        <v>53000</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>10100</v>
@@ -671,10 +671,10 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>61000</v>
+        <v>53000</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>22200</v>
+        <v>2030</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>85000</v>
@@ -713,7 +713,7 @@
         <v>62000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>22200</v>
+        <v>2030</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>120000</v>
